--- a/master/result/60_重生职场_复仇女王之路/60_重生职场_复仇女王之路.xlsx
+++ b/master/result/60_重生职场_复仇女王之路/60_重生职场_复仇女王之路.xlsx
@@ -397,555 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>desolate</v>
       </c>
       <c r="B2" t="str">
-        <v>desolate</v>
+        <v>/desolate/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>荒凉的</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>once</v>
       </c>
       <c r="B3" t="str">
-        <v>once</v>
+        <v>/once/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>一次</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>beautiful</v>
       </c>
       <c r="B4" t="str">
-        <v>beautiful</v>
+        <v>/ˈbjuːtɪfəl/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>美丽的</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>twelve</v>
       </c>
       <c r="B5" t="str">
-        <v>twelve</v>
+        <v>/twelve/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>十二</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>down</v>
       </c>
       <c r="B6" t="str">
-        <v>down</v>
+        <v>/down/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>向下</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>merit</v>
       </c>
       <c r="B7" t="str">
-        <v>merit</v>
+        <v>/merit/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>优点</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>ancestor</v>
       </c>
       <c r="B8" t="str">
-        <v>ancestor</v>
+        <v>/ˈænsestə/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>祖先</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>fellowship</v>
       </c>
       <c r="B9" t="str">
-        <v>fellowship</v>
+        <v>/fellowship/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>联谊会</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>typewriter</v>
       </c>
       <c r="B10" t="str">
-        <v>typewriter</v>
+        <v>/typewriter/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>打字机</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>missing</v>
       </c>
       <c r="B11" t="str">
-        <v>missing</v>
+        <v>/missing/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>缺失</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>hope</v>
       </c>
       <c r="B12" t="str">
-        <v>hope</v>
+        <v>/həʊp/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>希望</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>shopkeeper</v>
       </c>
       <c r="B13" t="str">
-        <v>shopkeeper</v>
+        <v>/shopkeeper/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>店主</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>conspicuous</v>
       </c>
       <c r="B14" t="str">
-        <v>conspicuous</v>
+        <v>/conspicuous/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>显眼的</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>arouse</v>
       </c>
       <c r="B15" t="str">
-        <v>arouse</v>
+        <v>/arouse/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>激励</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>mess</v>
       </c>
       <c r="B16" t="str">
-        <v>mess</v>
+        <v>/mess/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>搞乱</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>paper</v>
       </c>
       <c r="B17" t="str">
-        <v>paper</v>
+        <v>/paper/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>纸</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>linguistic</v>
       </c>
       <c r="B18" t="str">
-        <v>linguistic</v>
+        <v>/linguistic/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>语言</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>jolly</v>
       </c>
       <c r="B19" t="str">
-        <v>jolly</v>
+        <v>/jolly/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>欢乐的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>skeptical</v>
       </c>
       <c r="B20" t="str">
-        <v>skeptical</v>
+        <v>/skeptical/</v>
       </c>
       <c r="C20" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>怀疑</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>correspondent</v>
       </c>
       <c r="B21" t="str">
-        <v>correspondent</v>
+        <v>/correspondent/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>记者</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>refute</v>
       </c>
       <c r="B22" t="str">
-        <v>refute</v>
+        <v>/refute/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>反驳</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>despair</v>
       </c>
       <c r="B23" t="str">
-        <v>despair</v>
+        <v>/despair/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>绝望</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>ashamed</v>
       </c>
       <c r="B24" t="str">
-        <v>ashamed</v>
+        <v>/ashamed/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>羞耻</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>frank</v>
       </c>
       <c r="B25" t="str">
-        <v>frank</v>
+        <v>/frank/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>坦白的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>stability</v>
       </c>
       <c r="B26" t="str">
-        <v>stability</v>
+        <v>/stability/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>稳定</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>guest</v>
       </c>
       <c r="B27" t="str">
-        <v>guest</v>
+        <v>/guest/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>客人</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>know</v>
       </c>
       <c r="B28" t="str">
-        <v>know</v>
+        <v>/nəʊ/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>知道</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>wicked</v>
       </c>
       <c r="B29" t="str">
-        <v>wicked</v>
+        <v>/wicked/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>邪恶的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>greedy</v>
       </c>
       <c r="B30" t="str">
-        <v>greedy</v>
+        <v>/greedy/</v>
       </c>
       <c r="C30" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D30" t="str">
         <v>贪婪的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>dentist</v>
       </c>
       <c r="B31" t="str">
-        <v>dentist</v>
+        <v>/dentist/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>牙医</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>territory</v>
       </c>
       <c r="B32" t="str">
-        <v>territory</v>
+        <v>/territory/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>领土</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>radius</v>
       </c>
       <c r="B33" t="str">
-        <v>radius</v>
+        <v>/radius/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>半径</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>composite</v>
       </c>
       <c r="B34" t="str">
-        <v>composite</v>
+        <v>/composite/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>混合</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>many</v>
       </c>
       <c r="B35" t="str">
-        <v>many</v>
+        <v>/many/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>许多</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>mankind</v>
       </c>
       <c r="B36" t="str">
-        <v>mankind</v>
+        <v>/mankind/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>人类</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>musician</v>
       </c>
       <c r="B37" t="str">
-        <v>musician</v>
+        <v>/musician/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>音乐家</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>bounce</v>
       </c>
       <c r="B38" t="str">
-        <v>bounce</v>
+        <v>/bounce/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>弹起</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>umbrella</v>
       </c>
       <c r="B39" t="str">
-        <v>umbrella</v>
+        <v>/umbrella/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>伞</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>recipient</v>
       </c>
       <c r="B40" t="str">
-        <v>recipient</v>
+        <v>/recipient/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>接收</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>gasoline</v>
       </c>
       <c r="B41" t="str">
-        <v>gasoline</v>
+        <v>/gasoline/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>汽油</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>chapter</v>
       </c>
       <c r="B42" t="str">
-        <v>chapter</v>
+        <v>/ˈtʃæptə/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>章节</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>surface</v>
       </c>
       <c r="B43" t="str">
-        <v>surface</v>
+        <v>/surface/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>表面</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>avail</v>
       </c>
       <c r="B44" t="str">
-        <v>avail</v>
+        <v>/avail/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>效用</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>slum</v>
       </c>
       <c r="B45" t="str">
-        <v>slum</v>
+        <v>/slum/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>贫民窟</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>excuse</v>
       </c>
       <c r="B46" t="str">
-        <v>excuse</v>
+        <v>/ɪkˈskjuːz/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>借口</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>homework</v>
       </c>
       <c r="B47" t="str">
-        <v>homework</v>
+        <v>/homework/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>作业</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>brittle</v>
       </c>
       <c r="B48" t="str">
-        <v>brittle</v>
+        <v>/brittle/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>脆弱</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>fond</v>
       </c>
       <c r="B49" t="str">
-        <v>fond</v>
+        <v>/fond/</v>
       </c>
       <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
         <v>喜爱</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>